--- a/output/quickfixclose_portfolio_daily.xlsx
+++ b/output/quickfixclose_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$182</f>
+              <f>'equity_curve'!$A$2:$A$184</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$182</f>
+              <f>'equity_curve'!$B$2:$B$184</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>489,473.14</t>
+          <t>504,201.14</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+389.47%</t>
+          <t>+404.20%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>504,386  (+404.39%)</t>
+          <t>520,101  (+420.10%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7,654  (14.9 pts of return)</t>
+          <t>8,175  (15.9 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7016.1x</t>
+          <t>7281.4x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12">
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3,897  (+1.63%)</t>
+          <t>3,965  (+1.63%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-27</t>
+          <t>2025-12-18 -&gt; 2026-07-29</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:H184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5126,6 +5126,62 @@
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
     </row>
+    <row r="183">
+      <c r="A183" s="4" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B183" s="5" t="n">
+        <v>498222.47</v>
+      </c>
+      <c r="C183" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D183" s="5" t="n">
+        <v>498222.47</v>
+      </c>
+      <c r="E183" t="n">
+        <v>0</v>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures short (risk 4,895)</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures exit_close (+8,749)</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B184" s="5" t="n">
+        <v>504201.14</v>
+      </c>
+      <c r="C184" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D184" s="5" t="n">
+        <v>504201.14</v>
+      </c>
+      <c r="E184" t="n">
+        <v>0</v>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>NY_Natural_Gas_Futures long (risk 4,982)</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>NY_Natural_Gas_Futures exit_close (+5,979)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5138,7 +5194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M104"/>
+  <dimension ref="A1:M106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10476,6 +10532,108 @@
         </is>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1.812</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H105" t="n">
+        <v>1.788</v>
+      </c>
+      <c r="I105" s="5" t="n">
+        <v>891375.33</v>
+      </c>
+      <c r="J105" s="5" t="n">
+        <v>12390.12</v>
+      </c>
+      <c r="K105" s="6" t="n">
+        <v>22147.33</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>913522.66</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>exit_close</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>NY_Natural_Gas_Futures</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H106" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I106" s="5" t="n">
+        <v>913522.66</v>
+      </c>
+      <c r="J106" s="5" t="n">
+        <v>12697.96</v>
+      </c>
+      <c r="K106" s="6" t="n">
+        <v>15237.56</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>928760.22</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>exit_close</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/quickfixclose_portfolio_daily.xlsx
+++ b/output/quickfixclose_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$184</f>
+              <f>'equity_curve'!$A$2:$A$185</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$184</f>
+              <f>'equity_curve'!$B$2:$B$185</f>
             </numRef>
           </val>
         </ser>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-29</t>
+          <t>2025-12-18 -&gt; 2026-07-30</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H184"/>
+  <dimension ref="A1:H185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5181,6 +5181,26 @@
           <t>NY_Natural_Gas_Futures exit_close (+5,979)</t>
         </is>
       </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="4" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B185" s="5" t="n">
+        <v>504201.14</v>
+      </c>
+      <c r="C185" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D185" s="5" t="n">
+        <v>504201.14</v>
+      </c>
+      <c r="E185" t="n">
+        <v>0</v>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
